--- a/config/grow_guide.xlsx
+++ b/config/grow_guide.xlsx
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>ハードステージ</t>
+          <t>困难关卡</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>更なる難易度に挑め！</t>
+          <t>挑战更高的难度！</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>ハードステージ</t>
+          <t>困难关卡</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>更なる難易度に挑め！</t>
+          <t>挑战更高的难度！</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ハードステージに50回挑戦</t>
+          <t>挑战50次高难度关卡</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>アリーナ</t>
+          <t>竞技场</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>危機を制して勇者となる！</t>
+          <t>克服危机成为勇者！</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>アリーナ</t>
+          <t>竞技场</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>危機を制して勇者となる！</t>
+          <t>克服危机成为勇者！</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>アリーナに20回挑戦</t>
+          <t>20次挑战竞技场</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>ダンジョン</t>
+          <t>地牢</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>挑戦で豪華報酬GET！</t>
+          <t>挑战获得丰厚奖励！</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>ダンジョン</t>
+          <t>地牢</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>挑戦で豪華報酬GET！</t>
+          <t>挑战获得丰厚奖励！</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ダンジョンに10回挑戦</t>
+          <t>挑战10次地牢</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>無限の旅路を制覇せよ！</t>
+          <t>征服无限之旅！</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>ギルド</t>
+          <t>公会</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ギルド加入で同志を求めよ！</t>
+          <t>加入公会，寻找志同道合的伙伴！</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>ギルド</t>
+          <t>公会</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ギルド加入で同志を求めよ！</t>
+          <t>加入公会，寻找志同道合的伙伴！</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>ギルドに10回寄付</t>
+          <t>向公会捐赠10次</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2741,14 +2741,14 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
+          <t>天赋强化</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>天賦強化</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>天賦強化</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Talent enhancement</t>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>仲間を強化で最強を目指せ！</t>
+          <t>强化伙伴，以最强为目标！</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2828,14 +2828,14 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
+          <t>天赋强化</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>天賦強化</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>天賦強化</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>Talent enhancement</t>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>仲間を強化で最強を目指せ！</t>
+          <t>强化伙伴，以最强为目标！</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>天賦PTを50使用</t>
+          <t>使用50个天赋PT</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2955,14 +2955,14 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
+          <t>日常任务</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>日常任務</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>日常任務</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>Daily Mission</t>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>千里の道も一歩から！</t>
+          <t>千里之行始于足下!</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3042,14 +3042,14 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
+          <t>日常任务</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>日常任務</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>日常任務</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>Daily Mission</t>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>千里の道も一歩から！</t>
+          <t>千里之行始于足下!</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>日常任務を20個クリア</t>
+          <t>完成20个日常任务</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>図鑑</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>仲間を収集し、能力を強化せよ！</t>
+          <t>收集伙伴并强化能力！</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>時空激戦</t>
+          <t>时空激战</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>時空激戦で豪華報酬をGET！</t>
+          <t>在时空激战中获得豪华奖励！</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>時空激戦</t>
+          <t>时空激战</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>時空激戦で豪華報酬をGET！</t>
+          <t>在时空激战中获得豪华奖励！</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>時空激戦に20回勝利</t>
+          <t>时空激战20次胜利</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>探査機</t>
+          <t>探测器</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>探査機</t>
+          <t>探测器</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P31" s="5" t="inlineStr">
         <is>
-          <t>探査機を5回強化</t>
+          <t>探测器强化5次</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
